--- a/backend/data/donglin/input/input_tb.xlsx
+++ b/backend/data/donglin/input/input_tb.xlsx
@@ -462,7 +462,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>江苏大王通风机械有限公司 - 科目余额表</t>
+          <t>甲公司（通风机械） - 科目余额表</t>
         </is>
       </c>
     </row>
@@ -476,10 +476,11 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>数据来源: 客户 ERP 导出 (东林审计底稿 donglin.xlsx 中 KM 科目表)</t>
-        </is>
-      </c>
-    </row>
+          <t>数据来源: 客户 ERP 导出 (甲所审计底稿 donglin.xlsx 中 KM 科目表)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -2101,7 +2102,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>大王工业风扇</t>
+          <t>甲公司工业风扇</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
